--- a/Reports/PR-5-Back-Office-Language-Test-Report.xlsx
+++ b/Reports/PR-5-Back-Office-Language-Test-Report.xlsx
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Results'!E2:E306,"Passed")</f>
+        <f>COUNTIF('Test Results'!E2:E321,"Passed")</f>
         <v/>
       </c>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Results'!E2:E306,"Failed")</f>
+        <f>COUNTIF('Test Results'!E2:E321,"Failed")</f>
         <v/>
       </c>
     </row>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF('Test Results'!E2:E306,"Skipped")</f>
+        <f>COUNTIF('Test Results'!E2:E321,"Skipped")</f>
         <v/>
       </c>
     </row>
